--- a/Result/profitability/8374.xlsx
+++ b/Result/profitability/8374.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM74"/>
+  <dimension ref="A1:AM75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -669,10 +669,10 @@
         <v>1.28</v>
       </c>
       <c r="M2" t="n">
-        <v>0.21375</v>
+        <v>0.25375</v>
       </c>
       <c r="N2" t="n">
-        <v>25.15125</v>
+        <v>25.0125</v>
       </c>
       <c r="O2" t="n">
         <v>1</v>
@@ -780,10 +780,10 @@
         <v>0.96</v>
       </c>
       <c r="M3" t="n">
-        <v>0.31625</v>
+        <v>0.3225</v>
       </c>
       <c r="N3" t="n">
-        <v>24.76</v>
+        <v>24.2275</v>
       </c>
       <c r="O3" t="n">
         <v>1</v>
@@ -899,10 +899,10 @@
         <v>1.1</v>
       </c>
       <c r="M4" t="n">
-        <v>0.4025</v>
+        <v>0.43</v>
       </c>
       <c r="N4" t="n">
-        <v>24.22875</v>
+        <v>23.67125</v>
       </c>
       <c r="O4" t="n">
         <v>1</v>
@@ -1018,10 +1018,10 @@
         <v>-0.68</v>
       </c>
       <c r="M5" t="n">
-        <v>0.2875</v>
+        <v>0.315</v>
       </c>
       <c r="N5" t="n">
-        <v>23.30125</v>
+        <v>22.77625</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -1137,10 +1137,10 @@
         <v>0.55</v>
       </c>
       <c r="M6" t="n">
-        <v>0.32625</v>
+        <v>0.35625</v>
       </c>
       <c r="N6" t="n">
-        <v>23.0025</v>
+        <v>22.69375</v>
       </c>
       <c r="O6" t="n">
         <v>1</v>
@@ -1152,7 +1152,7 @@
         <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S6" t="n">
         <v>1</v>
@@ -1264,10 +1264,10 @@
         <v>0.7</v>
       </c>
       <c r="M7" t="n">
-        <v>0.38625</v>
+        <v>0.6000000000000001</v>
       </c>
       <c r="N7" t="n">
-        <v>22.45125</v>
+        <v>22.87</v>
       </c>
       <c r="O7" t="n">
         <v>1</v>
@@ -1391,10 +1391,10 @@
         <v>0.74</v>
       </c>
       <c r="M8" t="n">
-        <v>0.635</v>
+        <v>0.6387499999999999</v>
       </c>
       <c r="N8" t="n">
-        <v>23.645</v>
+        <v>23.41875</v>
       </c>
       <c r="O8" t="n">
         <v>1</v>
@@ -1899,7 +1899,7 @@
         <v>1.43</v>
       </c>
       <c r="M12" t="n">
-        <v>0.6525000000000001</v>
+        <v>0.6525</v>
       </c>
       <c r="N12" t="n">
         <v>21.4675</v>
@@ -2026,7 +2026,7 @@
         <v>1.32</v>
       </c>
       <c r="M13" t="n">
-        <v>0.9025000000000001</v>
+        <v>0.9025</v>
       </c>
       <c r="N13" t="n">
         <v>21.6925</v>
@@ -9830,6 +9830,133 @@
       </c>
       <c r="AM74" t="n">
         <v>115.1</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>8374</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>115.2Q</t>
+        </is>
+      </c>
+      <c r="C75" t="n">
+        <v>1633</v>
+      </c>
+      <c r="D75" t="n">
+        <v>1255</v>
+      </c>
+      <c r="E75" t="n">
+        <v>378</v>
+      </c>
+      <c r="F75" t="n">
+        <v>23.16</v>
+      </c>
+      <c r="G75" t="n">
+        <v>132</v>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>8.08%</t>
+        </is>
+      </c>
+      <c r="I75" t="n">
+        <v>-9</v>
+      </c>
+      <c r="J75" t="n">
+        <v>123</v>
+      </c>
+      <c r="K75" t="n">
+        <v>51</v>
+      </c>
+      <c r="L75" t="n">
+        <v>0.46</v>
+      </c>
+      <c r="M75" t="n">
+        <v>0.11125</v>
+      </c>
+      <c r="N75" t="n">
+        <v>25.03</v>
+      </c>
+      <c r="O75" t="n">
+        <v>1</v>
+      </c>
+      <c r="P75" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q75" t="n">
+        <v>1</v>
+      </c>
+      <c r="R75" t="n">
+        <v>0</v>
+      </c>
+      <c r="S75" t="n">
+        <v>1</v>
+      </c>
+      <c r="T75" t="n">
+        <v>0</v>
+      </c>
+      <c r="U75" t="n">
+        <v>0</v>
+      </c>
+      <c r="V75" t="n">
+        <v>115.2</v>
+      </c>
+      <c r="W75" t="n">
+        <v>0.03000000000000003</v>
+      </c>
+      <c r="X75" t="n">
+        <v>0.06976744186046524</v>
+      </c>
+      <c r="Y75" t="n">
+        <v>-1.809999999999999</v>
+      </c>
+      <c r="Z75" t="n">
+        <v>-0.07248698438125745</v>
+      </c>
+      <c r="AA75" t="n">
+        <v>0.22</v>
+      </c>
+      <c r="AB75" t="n">
+        <v>0.9166666666666667</v>
+      </c>
+      <c r="AC75" t="n">
+        <v>-4.199999999999999</v>
+      </c>
+      <c r="AD75" t="n">
+        <v>-0.1535087719298245</v>
+      </c>
+      <c r="AE75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ75" t="inlineStr">
+        <is>
+          <t>EPS成長 / 毛利率衰退</t>
+        </is>
+      </c>
+      <c r="AK75" t="n">
+        <v>115</v>
+      </c>
+      <c r="AL75" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM75" t="n">
+        <v>115.2</v>
       </c>
     </row>
   </sheetData>
